--- a/Contracts/basketball_reference_contracts_with_teams.xlsx
+++ b/Contracts/basketball_reference_contracts_with_teams.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6402" uniqueCount="1709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6400" uniqueCount="1708">
   <si>
     <t>Rk</t>
   </si>
@@ -1048,7 +1048,7 @@
     <t>Ben Saraf</t>
   </si>
   <si>
-    <t>Pacome Dadiet</t>
+    <t>Pacôme Dadiet</t>
   </si>
   <si>
     <t>Danny Wolf</t>
@@ -1132,7 +1132,7 @@
     <t>Keon Johnson</t>
   </si>
   <si>
-    <t>Vit Krejci</t>
+    <t>Vít Krejčí</t>
   </si>
   <si>
     <t>Neemias Queta</t>
@@ -1153,7 +1153,7 @@
     <t>Ryan Kalkbrenner</t>
   </si>
   <si>
-    <t>Dante Exum</t>
+    <t>Danté Exum</t>
   </si>
   <si>
     <t>Anthony Gill</t>
@@ -4823,9 +4823,6 @@
   </si>
   <si>
     <t>$10,748,860</t>
-  </si>
-  <si>
-    <t>$9,439,024</t>
   </si>
   <si>
     <t>$10,302,446</t>
@@ -10832,17 +10829,14 @@
       <c r="D185" t="s">
         <v>647</v>
       </c>
-      <c r="E185" t="s">
-        <v>918</v>
-      </c>
       <c r="J185" t="s">
         <v>647</v>
       </c>
       <c r="K185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L185" t="s">
-        <v>1593</v>
+        <v>647</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -10897,7 +10891,7 @@
         <v>4</v>
       </c>
       <c r="L187" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -10923,7 +10917,7 @@
         <v>2</v>
       </c>
       <c r="L188" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -10949,7 +10943,7 @@
         <v>2</v>
       </c>
       <c r="L189" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -11004,7 +10998,7 @@
         <v>2</v>
       </c>
       <c r="L191" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -11030,7 +11024,7 @@
         <v>2</v>
       </c>
       <c r="L192" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -11082,7 +11076,7 @@
         <v>3</v>
       </c>
       <c r="L194" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -11114,7 +11108,7 @@
         <v>4</v>
       </c>
       <c r="L195" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -11178,7 +11172,7 @@
         <v>5</v>
       </c>
       <c r="L197" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -11227,7 +11221,7 @@
         <v>2</v>
       </c>
       <c r="L199" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -11282,7 +11276,7 @@
         <v>4</v>
       </c>
       <c r="L201" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -11334,7 +11328,7 @@
         <v>3</v>
       </c>
       <c r="L203" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -11516,7 +11510,7 @@
         <v>2</v>
       </c>
       <c r="L210" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -11545,7 +11539,7 @@
         <v>3</v>
       </c>
       <c r="L211" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -11609,7 +11603,7 @@
         <v>5</v>
       </c>
       <c r="L213" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -11670,7 +11664,7 @@
         <v>4</v>
       </c>
       <c r="L215" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -11719,7 +11713,7 @@
         <v>2</v>
       </c>
       <c r="L217" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -11777,7 +11771,7 @@
         <v>3</v>
       </c>
       <c r="L219" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -11881,7 +11875,7 @@
         <v>4</v>
       </c>
       <c r="L223" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -11982,7 +11976,7 @@
         <v>2</v>
       </c>
       <c r="L227" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -12040,7 +12034,7 @@
         <v>6</v>
       </c>
       <c r="L229" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -12069,7 +12063,7 @@
         <v>3</v>
       </c>
       <c r="L230" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -12147,7 +12141,7 @@
         <v>4</v>
       </c>
       <c r="L233" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -12274,7 +12268,7 @@
         <v>2</v>
       </c>
       <c r="L238" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -12300,7 +12294,7 @@
         <v>2</v>
       </c>
       <c r="L239" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -12329,7 +12323,7 @@
         <v>3</v>
       </c>
       <c r="L240" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -12361,7 +12355,7 @@
         <v>4</v>
       </c>
       <c r="L241" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -12465,7 +12459,7 @@
         <v>2</v>
       </c>
       <c r="L245" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -12494,7 +12488,7 @@
         <v>3</v>
       </c>
       <c r="L246" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -12526,7 +12520,7 @@
         <v>4</v>
       </c>
       <c r="L247" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -12552,7 +12546,7 @@
         <v>2</v>
       </c>
       <c r="L248" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -12578,7 +12572,7 @@
         <v>2</v>
       </c>
       <c r="L249" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -12650,7 +12644,7 @@
         <v>2</v>
       </c>
       <c r="L252" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="253" spans="1:12">
@@ -12676,7 +12670,7 @@
         <v>2</v>
       </c>
       <c r="L253" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="254" spans="1:12">
@@ -12728,7 +12722,7 @@
         <v>3</v>
       </c>
       <c r="L255" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="256" spans="1:12">
@@ -12760,7 +12754,7 @@
         <v>4</v>
       </c>
       <c r="L256" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="257" spans="1:12">
@@ -12786,7 +12780,7 @@
         <v>2</v>
       </c>
       <c r="L257" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="258" spans="1:12">
@@ -12884,7 +12878,7 @@
         <v>2</v>
       </c>
       <c r="L261" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="262" spans="1:12">
@@ -12910,7 +12904,7 @@
         <v>2</v>
       </c>
       <c r="L262" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="263" spans="1:12">
@@ -12939,7 +12933,7 @@
         <v>3</v>
       </c>
       <c r="L263" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="264" spans="1:12">
@@ -12971,7 +12965,7 @@
         <v>4</v>
       </c>
       <c r="L264" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="265" spans="1:12">
@@ -12997,7 +12991,7 @@
         <v>2</v>
       </c>
       <c r="L265" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="266" spans="1:12">
@@ -13115,7 +13109,7 @@
         <v>2</v>
       </c>
       <c r="L270" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="271" spans="1:12">
@@ -13167,7 +13161,7 @@
         <v>3</v>
       </c>
       <c r="L272" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="273" spans="1:12">
@@ -13205,7 +13199,7 @@
         <v>6</v>
       </c>
       <c r="L273" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="274" spans="1:12">
@@ -13237,7 +13231,7 @@
         <v>4</v>
       </c>
       <c r="L274" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="275" spans="1:12">
@@ -13286,7 +13280,7 @@
         <v>2</v>
       </c>
       <c r="L276" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="277" spans="1:12">
@@ -13338,7 +13332,7 @@
         <v>3</v>
       </c>
       <c r="L278" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="279" spans="1:12">
@@ -13370,7 +13364,7 @@
         <v>4</v>
       </c>
       <c r="L279" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="280" spans="1:12">
@@ -13454,7 +13448,7 @@
         <v>5</v>
       </c>
       <c r="L282" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="283" spans="1:12">
@@ -13483,7 +13477,7 @@
         <v>3</v>
       </c>
       <c r="L283" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="284" spans="1:12">
@@ -13515,7 +13509,7 @@
         <v>4</v>
       </c>
       <c r="L284" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="285" spans="1:12">
@@ -13564,7 +13558,7 @@
         <v>2</v>
       </c>
       <c r="L286" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="287" spans="1:12">
@@ -13590,7 +13584,7 @@
         <v>2</v>
       </c>
       <c r="L287" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="288" spans="1:12">
@@ -13619,7 +13613,7 @@
         <v>3</v>
       </c>
       <c r="L288" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="289" spans="1:12">
@@ -13651,7 +13645,7 @@
         <v>4</v>
       </c>
       <c r="L289" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="290" spans="1:12">
@@ -13703,7 +13697,7 @@
         <v>3</v>
       </c>
       <c r="L291" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="292" spans="1:12">
@@ -13787,7 +13781,7 @@
         <v>4</v>
       </c>
       <c r="L294" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="295" spans="1:12">
@@ -13813,7 +13807,7 @@
         <v>2</v>
       </c>
       <c r="L295" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="296" spans="1:12">
@@ -13845,7 +13839,7 @@
         <v>4</v>
       </c>
       <c r="L296" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="297" spans="1:12">
@@ -13874,7 +13868,7 @@
         <v>3</v>
       </c>
       <c r="L297" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="298" spans="1:12">
@@ -13900,7 +13894,7 @@
         <v>2</v>
       </c>
       <c r="L298" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="299" spans="1:12">
@@ -13926,7 +13920,7 @@
         <v>2</v>
       </c>
       <c r="L299" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="300" spans="1:12">
@@ -13984,7 +13978,7 @@
         <v>4</v>
       </c>
       <c r="L301" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="302" spans="1:12">
@@ -14013,7 +14007,7 @@
         <v>3</v>
       </c>
       <c r="L302" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="303" spans="1:12">
@@ -14039,7 +14033,7 @@
         <v>2</v>
       </c>
       <c r="L303" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="304" spans="1:12">
@@ -14065,7 +14059,7 @@
         <v>2</v>
       </c>
       <c r="L304" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="305" spans="1:12">
@@ -14097,7 +14091,7 @@
         <v>4</v>
       </c>
       <c r="L305" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="306" spans="1:12">
@@ -14126,7 +14120,7 @@
         <v>3</v>
       </c>
       <c r="L306" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="307" spans="1:12">
@@ -14175,7 +14169,7 @@
         <v>2</v>
       </c>
       <c r="L308" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="309" spans="1:12">
@@ -14207,7 +14201,7 @@
         <v>4</v>
       </c>
       <c r="L309" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="310" spans="1:12">
@@ -14236,7 +14230,7 @@
         <v>3</v>
       </c>
       <c r="L310" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="311" spans="1:12">
@@ -14262,7 +14256,7 @@
         <v>2</v>
       </c>
       <c r="L311" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="312" spans="1:12">
@@ -14317,7 +14311,7 @@
         <v>4</v>
       </c>
       <c r="L313" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="314" spans="1:12">
@@ -14346,7 +14340,7 @@
         <v>3</v>
       </c>
       <c r="L314" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="315" spans="1:12">
@@ -14372,7 +14366,7 @@
         <v>2</v>
       </c>
       <c r="L315" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="316" spans="1:12">
@@ -14404,7 +14398,7 @@
         <v>4</v>
       </c>
       <c r="L316" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="317" spans="1:12">
@@ -14465,7 +14459,7 @@
         <v>3</v>
       </c>
       <c r="L318" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="319" spans="1:12">
@@ -14491,7 +14485,7 @@
         <v>2</v>
       </c>
       <c r="L319" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="320" spans="1:12">
@@ -14517,7 +14511,7 @@
         <v>2</v>
       </c>
       <c r="L320" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="321" spans="1:12">
@@ -14575,7 +14569,7 @@
         <v>3</v>
       </c>
       <c r="L322" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="323" spans="1:12">
@@ -14630,7 +14624,7 @@
         <v>4</v>
       </c>
       <c r="L324" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="325" spans="1:12">
@@ -14659,7 +14653,7 @@
         <v>3</v>
       </c>
       <c r="L325" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="326" spans="1:12">
@@ -14708,7 +14702,7 @@
         <v>2</v>
       </c>
       <c r="L327" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="328" spans="1:12">
@@ -14740,7 +14734,7 @@
         <v>4</v>
       </c>
       <c r="L328" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="329" spans="1:12">
@@ -14769,7 +14763,7 @@
         <v>3</v>
       </c>
       <c r="L329" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="330" spans="1:12">
@@ -14801,7 +14795,7 @@
         <v>4</v>
       </c>
       <c r="L330" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="331" spans="1:12">
@@ -14827,7 +14821,7 @@
         <v>2</v>
       </c>
       <c r="L331" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="332" spans="1:12">
@@ -14859,7 +14853,7 @@
         <v>4</v>
       </c>
       <c r="L332" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="333" spans="1:12">
@@ -14891,7 +14885,7 @@
         <v>4</v>
       </c>
       <c r="L333" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="334" spans="1:12">
@@ -14946,7 +14940,7 @@
         <v>4</v>
       </c>
       <c r="L335" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="336" spans="1:12">
@@ -14995,7 +14989,7 @@
         <v>2</v>
       </c>
       <c r="L337" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="338" spans="1:12">
@@ -15021,7 +15015,7 @@
         <v>2</v>
       </c>
       <c r="L338" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="339" spans="1:12">
@@ -15050,7 +15044,7 @@
         <v>3</v>
       </c>
       <c r="L339" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="340" spans="1:12">
@@ -15079,7 +15073,7 @@
         <v>3</v>
       </c>
       <c r="L340" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="341" spans="1:12">
@@ -15105,7 +15099,7 @@
         <v>2</v>
       </c>
       <c r="L341" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="342" spans="1:12">
@@ -15134,7 +15128,7 @@
         <v>3</v>
       </c>
       <c r="L342" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="343" spans="1:12">
@@ -15163,7 +15157,7 @@
         <v>3</v>
       </c>
       <c r="L343" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="344" spans="1:12">
@@ -15238,7 +15232,7 @@
         <v>4</v>
       </c>
       <c r="L346" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="347" spans="1:12">
@@ -15264,7 +15258,7 @@
         <v>2</v>
       </c>
       <c r="L347" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="348" spans="1:12">
@@ -15290,7 +15284,7 @@
         <v>2</v>
       </c>
       <c r="L348" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="349" spans="1:12">
@@ -15316,7 +15310,7 @@
         <v>2</v>
       </c>
       <c r="L349" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="350" spans="1:12">
@@ -15342,7 +15336,7 @@
         <v>2</v>
       </c>
       <c r="L350" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="351" spans="1:12">
@@ -15371,7 +15365,7 @@
         <v>3</v>
       </c>
       <c r="L351" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="352" spans="1:12">
@@ -15397,7 +15391,7 @@
         <v>2</v>
       </c>
       <c r="L352" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="353" spans="1:12">
@@ -15426,7 +15420,7 @@
         <v>3</v>
       </c>
       <c r="L353" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="354" spans="1:12">
@@ -15478,7 +15472,7 @@
         <v>3</v>
       </c>
       <c r="L355" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="356" spans="1:12">
@@ -15527,7 +15521,7 @@
         <v>3</v>
       </c>
       <c r="L357" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="358" spans="1:12">
@@ -15550,7 +15544,7 @@
         <v>2</v>
       </c>
       <c r="L358" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="359" spans="1:12">
@@ -15585,7 +15579,7 @@
         <v>5</v>
       </c>
       <c r="L359" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="360" spans="1:12">
@@ -15611,7 +15605,7 @@
         <v>2</v>
       </c>
       <c r="L360" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="361" spans="1:12">
@@ -15666,7 +15660,7 @@
         <v>4</v>
       </c>
       <c r="L362" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="363" spans="1:12">
@@ -15698,7 +15692,7 @@
         <v>4</v>
       </c>
       <c r="L363" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="364" spans="1:12">
@@ -15982,13 +15976,13 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>380</v>
+        <v>152</v>
       </c>
       <c r="C376" t="s">
         <v>479</v>
       </c>
       <c r="D376" t="s">
-        <v>796</v>
+        <v>612</v>
       </c>
       <c r="J376" t="s">
         <v>796</v>
@@ -15997,7 +15991,7 @@
         <v>1</v>
       </c>
       <c r="L376" t="s">
-        <v>796</v>
+        <v>612</v>
       </c>
     </row>
     <row r="377" spans="1:12">
@@ -16005,13 +15999,13 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="C377" t="s">
         <v>479</v>
       </c>
       <c r="D377" t="s">
-        <v>612</v>
+        <v>796</v>
       </c>
       <c r="J377" t="s">
         <v>796</v>
@@ -16020,7 +16014,7 @@
         <v>1</v>
       </c>
       <c r="L377" t="s">
-        <v>612</v>
+        <v>796</v>
       </c>
     </row>
     <row r="378" spans="1:12">
@@ -16549,7 +16543,7 @@
         <v>3</v>
       </c>
       <c r="L400" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="401" spans="1:12">
@@ -16615,7 +16609,7 @@
         <v>2</v>
       </c>
       <c r="L403" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="404" spans="1:12">
@@ -16673,7 +16667,7 @@
         <v>5</v>
       </c>
       <c r="L405" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="406" spans="1:12">
@@ -16745,7 +16739,7 @@
         <v>2</v>
       </c>
       <c r="L408" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="409" spans="1:12">
@@ -16771,7 +16765,7 @@
         <v>2</v>
       </c>
       <c r="L409" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="410" spans="1:12">
@@ -16820,7 +16814,7 @@
         <v>2</v>
       </c>
       <c r="L411" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="412" spans="1:12">
@@ -16892,7 +16886,7 @@
         <v>2</v>
       </c>
       <c r="L414" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="415" spans="1:12">
@@ -16915,7 +16909,7 @@
         <v>2</v>
       </c>
       <c r="L415" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="416" spans="1:12">
@@ -16938,7 +16932,7 @@
         <v>2</v>
       </c>
       <c r="L416" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="417" spans="1:12">
@@ -16961,7 +16955,7 @@
         <v>2</v>
       </c>
       <c r="L417" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="418" spans="1:12">
@@ -16984,7 +16978,7 @@
         <v>2</v>
       </c>
       <c r="L418" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="419" spans="1:12">
@@ -17027,7 +17021,7 @@
         <v>2</v>
       </c>
       <c r="L420" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="421" spans="1:12">
@@ -17085,7 +17079,7 @@
         <v>3</v>
       </c>
       <c r="L422" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="423" spans="1:12">
@@ -17183,7 +17177,7 @@
         <v>3</v>
       </c>
       <c r="L426" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="427" spans="1:12">
@@ -17252,7 +17246,7 @@
         <v>2</v>
       </c>
       <c r="L429" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="430" spans="1:12">
@@ -17281,7 +17275,7 @@
         <v>3</v>
       </c>
       <c r="L430" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="431" spans="1:12">
@@ -17307,7 +17301,7 @@
         <v>2</v>
       </c>
       <c r="L431" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="432" spans="1:12">
@@ -17333,7 +17327,7 @@
         <v>2</v>
       </c>
       <c r="L432" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="433" spans="1:12">
@@ -17362,7 +17356,7 @@
         <v>3</v>
       </c>
       <c r="L433" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="434" spans="1:12">
@@ -17411,7 +17405,7 @@
         <v>2</v>
       </c>
       <c r="L435" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="436" spans="1:12">
@@ -17463,7 +17457,7 @@
         <v>3</v>
       </c>
       <c r="L437" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="438" spans="1:12">
@@ -17492,7 +17486,7 @@
         <v>3</v>
       </c>
       <c r="L438" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="439" spans="1:12">
@@ -17521,7 +17515,7 @@
         <v>3</v>
       </c>
       <c r="L439" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="440" spans="1:12">
@@ -17596,7 +17590,7 @@
         <v>3</v>
       </c>
       <c r="L442" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="443" spans="1:12">
@@ -17642,7 +17636,7 @@
         <v>2</v>
       </c>
       <c r="L444" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="445" spans="1:12">
@@ -17668,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="L445" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="446" spans="1:12">
@@ -17691,7 +17685,7 @@
         <v>2</v>
       </c>
       <c r="L446" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="447" spans="1:12">
@@ -17723,7 +17717,7 @@
         <v>4</v>
       </c>
       <c r="L447" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="448" spans="1:12">
@@ -17755,7 +17749,7 @@
         <v>4</v>
       </c>
       <c r="L448" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="449" spans="1:12">
@@ -17784,7 +17778,7 @@
         <v>3</v>
       </c>
       <c r="L449" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="450" spans="1:12">
@@ -17816,7 +17810,7 @@
         <v>4</v>
       </c>
       <c r="L450" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="451" spans="1:12">
@@ -17848,7 +17842,7 @@
         <v>4</v>
       </c>
       <c r="L451" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="452" spans="1:12">
@@ -17880,7 +17874,7 @@
         <v>4</v>
       </c>
       <c r="L452" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="453" spans="1:12">
@@ -17909,7 +17903,7 @@
         <v>3</v>
       </c>
       <c r="L453" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="454" spans="1:12">
@@ -17941,7 +17935,7 @@
         <v>4</v>
       </c>
       <c r="L454" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="455" spans="1:12">
@@ -17973,7 +17967,7 @@
         <v>4</v>
       </c>
       <c r="L455" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="456" spans="1:12">
@@ -18028,7 +18022,7 @@
         <v>4</v>
       </c>
       <c r="L457" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="458" spans="1:12">
@@ -18618,7 +18612,7 @@
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -18647,7 +18641,7 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -18719,7 +18713,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -18745,7 +18739,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -18820,7 +18814,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -18852,7 +18846,7 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
   </sheetData>
@@ -19056,7 +19050,7 @@
         <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -19082,7 +19076,7 @@
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -19108,7 +19102,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -19209,7 +19203,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
   </sheetData>
@@ -19954,7 +19948,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -20003,7 +19997,7 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -20029,7 +20023,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -20058,7 +20052,7 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -20087,7 +20081,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -20119,7 +20113,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -20495,7 +20489,7 @@
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -20550,7 +20544,7 @@
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -20576,7 +20570,7 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -20634,7 +20628,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -20663,7 +20657,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
   </sheetData>
@@ -20997,7 +20991,7 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -21046,7 +21040,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -21075,7 +21069,7 @@
         <v>3</v>
       </c>
       <c r="L15" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -21104,7 +21098,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
   </sheetData>
@@ -21301,17 +21295,14 @@
       <c r="D7" t="s">
         <v>647</v>
       </c>
-      <c r="E7" t="s">
-        <v>918</v>
-      </c>
       <c r="J7" t="s">
         <v>647</v>
       </c>
       <c r="K7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>1593</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -21389,7 +21380,7 @@
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -21418,7 +21409,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -21450,7 +21441,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -21482,7 +21473,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -21514,7 +21505,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -21566,7 +21557,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -21592,7 +21583,7 @@
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -21621,7 +21612,7 @@
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -21955,7 +21946,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -21984,7 +21975,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -22010,7 +22001,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -22042,7 +22033,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -22071,7 +22062,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -22117,7 +22108,7 @@
         <v>2</v>
       </c>
       <c r="L16" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
   </sheetData>
@@ -22382,7 +22373,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -22437,7 +22428,7 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -22463,7 +22454,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -22489,7 +22480,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -22515,7 +22506,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -22550,7 +22541,7 @@
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -22613,7 +22604,7 @@
         <v>2</v>
       </c>
       <c r="L18" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -22662,7 +22653,7 @@
         <v>2</v>
       </c>
       <c r="L20" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
   </sheetData>
@@ -22948,7 +22939,7 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -22977,7 +22968,7 @@
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -23049,7 +23040,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -23413,7 +23404,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -23445,7 +23436,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -23511,7 +23502,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -23811,7 +23802,7 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -23837,7 +23828,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -23892,7 +23883,7 @@
         <v>4</v>
       </c>
       <c r="L11" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -23918,7 +23909,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -23947,7 +23938,7 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -23996,7 +23987,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -24028,7 +24019,7 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -24331,7 +24322,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -24360,7 +24351,7 @@
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -24435,7 +24426,7 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -24843,7 +24834,7 @@
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -24869,7 +24860,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -24898,7 +24889,7 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -24930,7 +24921,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -24959,7 +24950,7 @@
         <v>3</v>
       </c>
       <c r="L15" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -24988,7 +24979,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -25289,7 +25280,7 @@
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -25315,7 +25306,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -25341,7 +25332,7 @@
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -25393,7 +25384,7 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -25425,7 +25416,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -25457,7 +25448,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
   </sheetData>
@@ -25725,7 +25716,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -25800,7 +25791,7 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -25826,7 +25817,7 @@
         <v>3</v>
       </c>
       <c r="L13" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -25858,7 +25849,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
   </sheetData>
@@ -26135,7 +26126,7 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -26196,7 +26187,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -26227,13 +26218,13 @@
         <v>375</v>
       </c>
       <c r="B13" t="s">
-        <v>380</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
         <v>479</v>
       </c>
       <c r="D13" t="s">
-        <v>796</v>
+        <v>612</v>
       </c>
       <c r="J13" t="s">
         <v>796</v>
@@ -26242,7 +26233,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>796</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -26250,13 +26241,13 @@
         <v>376</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="C14" t="s">
         <v>479</v>
       </c>
       <c r="D14" t="s">
-        <v>612</v>
+        <v>796</v>
       </c>
       <c r="J14" t="s">
         <v>796</v>
@@ -26265,7 +26256,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>612</v>
+        <v>796</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -26317,7 +26308,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -26349,7 +26340,7 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -26672,7 +26663,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -26701,7 +26692,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -26733,7 +26724,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -26759,7 +26750,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -26785,7 +26776,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -26843,7 +26834,7 @@
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -27149,7 +27140,7 @@
         <v>3</v>
       </c>
       <c r="L8" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -27181,7 +27172,7 @@
         <v>4</v>
       </c>
       <c r="L9" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -27302,7 +27293,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
   </sheetData>
@@ -27663,7 +27654,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -27992,7 +27983,7 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -28018,7 +28009,7 @@
         <v>2</v>
       </c>
       <c r="L8" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -28047,7 +28038,7 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -28073,7 +28064,7 @@
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -28142,7 +28133,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -28168,7 +28159,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -28194,7 +28185,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -28217,7 +28208,7 @@
         <v>2</v>
       </c>
       <c r="L16" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
   </sheetData>
@@ -28480,7 +28471,7 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -28509,7 +28500,7 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -28535,7 +28526,7 @@
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -28558,7 +28549,7 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -28607,7 +28598,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
   </sheetData>
@@ -28823,7 +28814,7 @@
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -28878,7 +28869,7 @@
         <v>3</v>
       </c>
       <c r="L9" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -28927,7 +28918,7 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -29031,7 +29022,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -29060,7 +29051,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -29086,7 +29077,7 @@
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -29299,7 +29290,7 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -29325,7 +29316,7 @@
         <v>2</v>
       </c>
       <c r="L7" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -29380,7 +29371,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -29432,7 +29423,7 @@
         <v>3</v>
       </c>
       <c r="L11" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -29458,7 +29449,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -29490,7 +29481,7 @@
         <v>4</v>
       </c>
       <c r="L13" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -29519,7 +29510,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -29571,7 +29562,7 @@
         <v>3</v>
       </c>
       <c r="L16" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -29781,7 +29772,7 @@
         <v>4</v>
       </c>
       <c r="L5" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -29957,7 +29948,7 @@
         <v>4</v>
       </c>
       <c r="L12" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -29983,7 +29974,7 @@
         <v>2</v>
       </c>
       <c r="L13" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -30015,7 +30006,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -30070,7 +30061,7 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -30102,7 +30093,7 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -30128,7 +30119,7 @@
         <v>2</v>
       </c>
       <c r="L18" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -30499,7 +30490,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -30580,7 +30571,7 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -30632,7 +30623,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -30664,7 +30655,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -30707,7 +30698,7 @@
         <v>2</v>
       </c>
       <c r="L17" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
   </sheetData>
@@ -31050,7 +31041,7 @@
         <v>3</v>
       </c>
       <c r="L12" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -31105,7 +31096,7 @@
         <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -31183,7 +31174,7 @@
         <v>4</v>
       </c>
       <c r="L17" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -31215,7 +31206,7 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -31238,7 +31229,7 @@
         <v>2</v>
       </c>
       <c r="L19" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
   </sheetData>
@@ -31492,7 +31483,7 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -31541,7 +31532,7 @@
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -31653,7 +31644,7 @@
         <v>2</v>
       </c>
       <c r="L15" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -31685,7 +31676,7 @@
         <v>4</v>
       </c>
       <c r="L16" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -31991,7 +31982,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -32069,7 +32060,7 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -32121,7 +32112,7 @@
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -32444,7 +32435,7 @@
         <v>3</v>
       </c>
       <c r="L7" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -32482,7 +32473,7 @@
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -32534,7 +32525,7 @@
         <v>3</v>
       </c>
       <c r="L10" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -32560,7 +32551,7 @@
         <v>2</v>
       </c>
       <c r="L11" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -32632,7 +32623,7 @@
         <v>2</v>
       </c>
       <c r="L14" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
   </sheetData>
